--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run9/epoch_140/per_file_predictions_epoch_140.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run9/epoch_140/per_file_predictions_epoch_140.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="525">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,787 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.8479,0.0216,0.0414,0.0708</t>
-  </si>
-  <si>
-    <t>0.1121,0.0065,0.0156,0.9347</t>
-  </si>
-  <si>
-    <t>0.7644,0.0999,0.0354,0.0820</t>
-  </si>
-  <si>
-    <t>0.0360,0.0396,0.0143,0.9718</t>
-  </si>
-  <si>
-    <t>0.9952,0.0015,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9967,0.0005,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9948,0.0042,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9979,0.0008,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9980,0.0004,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9901,0.0151,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9954,0.0023,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9971,0.0019,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.8135,0.0710,0.1157,0.0225</t>
-  </si>
-  <si>
-    <t>0.0941,0.0755,0.8701,0.0024</t>
-  </si>
-  <si>
-    <t>0.0818,0.1401,0.7953,0.0011</t>
-  </si>
-  <si>
-    <t>0.2693,0.0184,0.8244,0.0058</t>
-  </si>
-  <si>
-    <t>0.4720,0.5018,0.0582,0.0164</t>
-  </si>
-  <si>
-    <t>0.0323,0.9642,0.0027,0.0012</t>
-  </si>
-  <si>
-    <t>0.1464,0.8926,0.0117,0.0009</t>
-  </si>
-  <si>
-    <t>0.6256,0.4866,0.0148,0.0008</t>
-  </si>
-  <si>
-    <t>0.1579,0.8845,0.0099,0.0008</t>
-  </si>
-  <si>
-    <t>0.0574,0.9569,0.0022,0.0004</t>
-  </si>
-  <si>
-    <t>0.2785,0.0022,0.0552,0.6900</t>
-  </si>
-  <si>
-    <t>0.3987,0.0275,0.1406,0.5106</t>
-  </si>
-  <si>
-    <t>0.0236,0.0030,0.9479,0.0783</t>
-  </si>
-  <si>
-    <t>0.3559,0.0076,0.8218,0.0013</t>
-  </si>
-  <si>
-    <t>0.2205,0.0160,0.8759,0.0028</t>
-  </si>
-  <si>
-    <t>0.0762,0.0065,0.9308,0.0152</t>
-  </si>
-  <si>
-    <t>0.0010,0.0014,0.9926,0.0114</t>
-  </si>
-  <si>
-    <t>0.6035,0.4991,0.0176,0.0010</t>
-  </si>
-  <si>
-    <t>0.7207,0.0709,0.3258,0.0052</t>
-  </si>
-  <si>
-    <t>0.0052,0.0094,0.9806,0.0135</t>
-  </si>
-  <si>
-    <t>0.0698,0.6023,0.3905,0.0035</t>
-  </si>
-  <si>
-    <t>0.8137,0.1904,0.0286,0.0112</t>
-  </si>
-  <si>
-    <t>0.7879,0.1493,0.1236,0.0073</t>
-  </si>
-  <si>
-    <t>0.5208,0.6071,0.0061,0.0005</t>
-  </si>
-  <si>
-    <t>0.0630,0.8151,0.3944,0.0041</t>
-  </si>
-  <si>
-    <t>0.0208,0.5032,0.0268,0.5296</t>
-  </si>
-  <si>
-    <t>0.0516,0.0196,0.9191,0.0170</t>
-  </si>
-  <si>
-    <t>0.0377,0.3305,0.8739,0.0194</t>
-  </si>
-  <si>
-    <t>0.0139,0.0110,0.9542,0.0464</t>
-  </si>
-  <si>
-    <t>0.0146,0.1491,0.9251,0.0041</t>
-  </si>
-  <si>
-    <t>0.0125,0.9328,0.0584,0.0099</t>
-  </si>
-  <si>
-    <t>0.0117,0.0124,0.9638,0.0224</t>
-  </si>
-  <si>
-    <t>0.1224,0.6758,0.0135,0.3292</t>
-  </si>
-  <si>
-    <t>0.0023,0.9589,0.0138,0.1449</t>
-  </si>
-  <si>
-    <t>0.0077,0.9656,0.0643,0.0076</t>
-  </si>
-  <si>
-    <t>0.0021,0.9625,0.0367,0.0578</t>
-  </si>
-  <si>
-    <t>0.0163,0.0558,0.9599,0.0092</t>
-  </si>
-  <si>
-    <t>0.0049,0.6080,0.9339,0.0008</t>
-  </si>
-  <si>
-    <t>0.0161,0.0084,0.9098,0.2330</t>
-  </si>
-  <si>
-    <t>0.0853,0.0274,0.8932,0.0151</t>
-  </si>
-  <si>
-    <t>0.0016,0.0054,0.9914,0.0041</t>
-  </si>
-  <si>
-    <t>0.0146,0.2032,0.9179,0.0027</t>
-  </si>
-  <si>
-    <t>0.9842,0.0098,0.0010,0.0012</t>
-  </si>
-  <si>
-    <t>0.9809,0.0145,0.0018,0.0010</t>
-  </si>
-  <si>
-    <t>0.9940,0.0011,0.0003,0.0011</t>
-  </si>
-  <si>
-    <t>0.0135,0.0331,0.9689,0.0092</t>
-  </si>
-  <si>
-    <t>0.9854,0.0135,0.0010,0.0005</t>
-  </si>
-  <si>
-    <t>0.9965,0.0019,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9774,0.0332,0.0018,0.0005</t>
-  </si>
-  <si>
-    <t>0.0009,0.8784,0.9614,0.0004</t>
-  </si>
-  <si>
-    <t>0.0005,0.0058,0.9917,0.0074</t>
-  </si>
-  <si>
-    <t>0.0189,0.1604,0.8832,0.0467</t>
-  </si>
-  <si>
-    <t>0.0004,0.6928,0.9881,0.0001</t>
-  </si>
-  <si>
-    <t>0.0021,0.0305,0.9873,0.0039</t>
-  </si>
-  <si>
-    <t>0.0926,0.9087,0.0197,0.0011</t>
-  </si>
-  <si>
-    <t>0.0124,0.9783,0.0031,0.0019</t>
-  </si>
-  <si>
-    <t>0.7235,0.0446,0.3036,0.0118</t>
-  </si>
-  <si>
-    <t>0.6244,0.1292,0.3641,0.0049</t>
-  </si>
-  <si>
-    <t>0.0023,0.0893,0.9873,0.0009</t>
-  </si>
-  <si>
-    <t>0.0018,0.9092,0.7963,0.0003</t>
-  </si>
-  <si>
-    <t>0.0127,0.6970,0.7724,0.0066</t>
-  </si>
-  <si>
-    <t>0.0008,0.9702,0.2743,0.0078</t>
-  </si>
-  <si>
-    <t>0.0008,0.9597,0.6349,0.0002</t>
-  </si>
-  <si>
-    <t>0.0665,0.0022,0.0084,0.9679</t>
-  </si>
-  <si>
-    <t>0.0061,0.0010,0.0008,0.9971</t>
-  </si>
-  <si>
-    <t>0.0050,0.0060,0.0006,0.9974</t>
-  </si>
-  <si>
-    <t>0.0166,0.0005,0.0045,0.9898</t>
-  </si>
-  <si>
-    <t>0.0111,0.0141,0.0037,0.9915</t>
-  </si>
-  <si>
-    <t>0.0055,0.0218,0.0026,0.9944</t>
-  </si>
-  <si>
-    <t>0.0004,0.9741,0.3992,0.0040</t>
-  </si>
-  <si>
-    <t>0.0050,0.8209,0.9043,0.0023</t>
-  </si>
-  <si>
-    <t>0.0148,0.7215,0.4742,0.0060</t>
-  </si>
-  <si>
-    <t>0.0136,0.7028,0.6682,0.0046</t>
-  </si>
-  <si>
-    <t>0.0013,0.8467,0.8730,0.0002</t>
-  </si>
-  <si>
-    <t>0.0122,0.5690,0.8504,0.0042</t>
-  </si>
-  <si>
-    <t>0.9953,0.0048,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9921,0.0043,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9749,0.0242,0.0011,0.0011</t>
-  </si>
-  <si>
-    <t>0.9939,0.0025,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9896,0.0090,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.9981,0.0012,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9833,0.0123,0.0009,0.0011</t>
-  </si>
-  <si>
-    <t>0.9944,0.0072,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9960,0.0017,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9965,0.0020,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9962,0.0006,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9979,0.0007,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9889,0.0049,0.0008,0.0012</t>
-  </si>
-  <si>
-    <t>0.9972,0.0005,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9935,0.0011,0.0000,0.0013</t>
+    <t>0,0,1,1</t>
+  </si>
+  <si>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0.6006,0.1898,0.0583,0.1620</t>
+  </si>
+  <si>
+    <t>0.0178,0.0010,0.0066,0.9883</t>
+  </si>
+  <si>
+    <t>0.4816,0.0686,0.0027,0.3929</t>
+  </si>
+  <si>
+    <t>0.0767,0.0298,0.0147,0.9557</t>
+  </si>
+  <si>
+    <t>0.9980,0.0009,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9969,0.0013,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9915,0.0073,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.9946,0.0031,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9946,0.0020,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.9950,0.0030,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9948,0.0016,0.0010,0.0005</t>
+  </si>
+  <si>
+    <t>0.9969,0.0015,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.5187,0.4602,0.0715,0.0066</t>
+  </si>
+  <si>
+    <t>0.1194,0.0251,0.8878,0.0011</t>
+  </si>
+  <si>
+    <t>0.5367,0.0420,0.5896,0.0149</t>
+  </si>
+  <si>
+    <t>0.1608,0.0133,0.8745,0.0156</t>
+  </si>
+  <si>
+    <t>0.8767,0.0415,0.0743,0.0055</t>
+  </si>
+  <si>
+    <t>0.0482,0.9524,0.0016,0.0017</t>
+  </si>
+  <si>
+    <t>0.2683,0.6574,0.1013,0.0016</t>
+  </si>
+  <si>
+    <t>0.5514,0.5770,0.0108,0.0016</t>
+  </si>
+  <si>
+    <t>0.3471,0.7909,0.0036,0.0008</t>
+  </si>
+  <si>
+    <t>0.0223,0.9744,0.0076,0.0004</t>
+  </si>
+  <si>
+    <t>0.4899,0.0787,0.5275,0.0358</t>
+  </si>
+  <si>
+    <t>0.6661,0.0265,0.3886,0.0271</t>
+  </si>
+  <si>
+    <t>0.0256,0.0144,0.9435,0.0293</t>
+  </si>
+  <si>
+    <t>0.3776,0.0161,0.6537,0.0332</t>
+  </si>
+  <si>
+    <t>0.0763,0.0054,0.9456,0.0080</t>
+  </si>
+  <si>
+    <t>0.0263,0.0016,0.9754,0.0092</t>
+  </si>
+  <si>
+    <t>0.0119,0.0071,0.9600,0.0300</t>
+  </si>
+  <si>
+    <t>0.3820,0.7304,0.0099,0.0029</t>
+  </si>
+  <si>
+    <t>0.5498,0.3385,0.1931,0.0125</t>
+  </si>
+  <si>
+    <t>0.0019,0.0121,0.9890,0.0032</t>
+  </si>
+  <si>
+    <t>0.0419,0.3022,0.7534,0.0030</t>
+  </si>
+  <si>
+    <t>0.8684,0.0899,0.0311,0.0174</t>
+  </si>
+  <si>
+    <t>0.4863,0.2076,0.3322,0.0055</t>
+  </si>
+  <si>
+    <t>0.6427,0.4565,0.0199,0.0031</t>
+  </si>
+  <si>
+    <t>0.0320,0.9056,0.3739,0.0026</t>
+  </si>
+  <si>
+    <t>0.0176,0.8009,0.2008,0.0432</t>
+  </si>
+  <si>
+    <t>0.0063,0.0019,0.9482,0.1215</t>
+  </si>
+  <si>
+    <t>0.0268,0.2394,0.8426,0.0629</t>
+  </si>
+  <si>
+    <t>0.0079,0.0063,0.9336,0.1498</t>
+  </si>
+  <si>
+    <t>0.1082,0.1017,0.8071,0.0172</t>
+  </si>
+  <si>
+    <t>0.0149,0.8930,0.1349,0.0006</t>
+  </si>
+  <si>
+    <t>0.0161,0.4615,0.8857,0.0057</t>
+  </si>
+  <si>
+    <t>0.0284,0.7968,0.0285,0.7155</t>
+  </si>
+  <si>
+    <t>0.0038,0.9466,0.0784,0.0847</t>
+  </si>
+  <si>
+    <t>0.0090,0.9649,0.0612,0.0035</t>
+  </si>
+  <si>
+    <t>0.0106,0.9540,0.0334,0.0334</t>
+  </si>
+  <si>
+    <t>0.0101,0.0517,0.9717,0.0070</t>
+  </si>
+  <si>
+    <t>0.0088,0.5819,0.9244,0.0011</t>
+  </si>
+  <si>
+    <t>0.0665,0.0162,0.9138,0.0065</t>
+  </si>
+  <si>
+    <t>0.0633,0.0033,0.9511,0.0110</t>
+  </si>
+  <si>
+    <t>0.0061,0.0036,0.9757,0.0362</t>
+  </si>
+  <si>
+    <t>0.0228,0.0768,0.9321,0.0023</t>
+  </si>
+  <si>
+    <t>0.9463,0.0681,0.0028,0.0018</t>
+  </si>
+  <si>
+    <t>0.9553,0.0440,0.0040,0.0019</t>
+  </si>
+  <si>
+    <t>0.9485,0.0377,0.0151,0.0022</t>
+  </si>
+  <si>
+    <t>0.0143,0.3011,0.9336,0.0070</t>
+  </si>
+  <si>
+    <t>0.9904,0.0019,0.0006,0.0019</t>
+  </si>
+  <si>
+    <t>0.9721,0.0347,0.0047,0.0003</t>
+  </si>
+  <si>
+    <t>0.9854,0.0120,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.0009,0.8332,0.9738,0.0006</t>
+  </si>
+  <si>
+    <t>0.0080,0.0242,0.9859,0.0024</t>
+  </si>
+  <si>
+    <t>0.0187,0.0326,0.9634,0.0063</t>
+  </si>
+  <si>
+    <t>0.0012,0.8491,0.9592,0.0004</t>
+  </si>
+  <si>
+    <t>0.0042,0.0263,0.9875,0.0018</t>
+  </si>
+  <si>
+    <t>0.2106,0.7342,0.0823,0.0047</t>
+  </si>
+  <si>
+    <t>0.0464,0.9496,0.0125,0.0006</t>
+  </si>
+  <si>
+    <t>0.6326,0.0623,0.4325,0.0019</t>
+  </si>
+  <si>
+    <t>0.6724,0.2685,0.1217,0.0374</t>
+  </si>
+  <si>
+    <t>0.0039,0.0464,0.9884,0.0016</t>
+  </si>
+  <si>
+    <t>0.0092,0.7672,0.7848,0.0028</t>
+  </si>
+  <si>
+    <t>0.0167,0.8625,0.3011,0.0064</t>
+  </si>
+  <si>
+    <t>0.0012,0.9851,0.1625,0.0007</t>
+  </si>
+  <si>
+    <t>0.0017,0.8743,0.9235,0.0010</t>
+  </si>
+  <si>
+    <t>0.0428,0.0016,0.0061,0.9800</t>
+  </si>
+  <si>
+    <t>0.0070,0.0088,0.0011,0.9960</t>
+  </si>
+  <si>
+    <t>0.0019,0.0155,0.0003,0.9984</t>
+  </si>
+  <si>
+    <t>0.0045,0.0014,0.1524,0.9646</t>
+  </si>
+  <si>
+    <t>0.0478,0.0025,0.0069,0.9764</t>
+  </si>
+  <si>
+    <t>0.0130,0.0081,0.0020,0.9929</t>
+  </si>
+  <si>
+    <t>0.0014,0.9517,0.8520,0.0005</t>
+  </si>
+  <si>
+    <t>0.0043,0.7290,0.8989,0.0005</t>
+  </si>
+  <si>
+    <t>0.0049,0.7519,0.8396,0.0008</t>
+  </si>
+  <si>
+    <t>0.0054,0.0753,0.9737,0.0015</t>
+  </si>
+  <si>
+    <t>0.0003,0.9490,0.9407,0.0000</t>
+  </si>
+  <si>
+    <t>0.0232,0.4541,0.7799,0.0074</t>
+  </si>
+  <si>
+    <t>0.9949,0.0041,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9843,0.0078,0.0016,0.0014</t>
+  </si>
+  <si>
+    <t>0.9893,0.0079,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9912,0.0043,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.9786,0.0204,0.0010,0.0011</t>
+  </si>
+  <si>
+    <t>0.9944,0.0059,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9950,0.0022,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9946,0.0030,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9946,0.0006,0.0001,0.0014</t>
+  </si>
+  <si>
+    <t>0.9962,0.0010,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9982,0.0007,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9974,0.0011,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9980,0.0005,0.0000,0.0002</t>
   </si>
   <si>
     <t>0.9973,0.0010,0.0001,0.0002</t>
   </si>
   <si>
-    <t>0.0057,0.0016,0.9872,0.0087</t>
-  </si>
-  <si>
-    <t>0.0749,0.0109,0.9274,0.0018</t>
-  </si>
-  <si>
-    <t>0.8605,0.0056,0.0365,0.0523</t>
-  </si>
-  <si>
-    <t>0.1944,0.0653,0.7598,0.0127</t>
-  </si>
-  <si>
-    <t>0.0915,0.9162,0.0053,0.0015</t>
-  </si>
-  <si>
-    <t>0.0943,0.9133,0.0047,0.0013</t>
-  </si>
-  <si>
-    <t>0.5065,0.6006,0.0062,0.0032</t>
-  </si>
-  <si>
-    <t>0.2863,0.7999,0.0031,0.0020</t>
-  </si>
-  <si>
-    <t>0.1274,0.9005,0.0037,0.0014</t>
-  </si>
-  <si>
-    <t>0.0276,0.9659,0.0050,0.0003</t>
-  </si>
-  <si>
-    <t>0.8507,0.2479,0.0012,0.0010</t>
-  </si>
-  <si>
-    <t>0.6510,0.2810,0.0559,0.0345</t>
-  </si>
-  <si>
-    <t>0.2321,0.0741,0.6892,0.0091</t>
-  </si>
-  <si>
-    <t>0.3677,0.4106,0.1981,0.0761</t>
-  </si>
-  <si>
-    <t>0.5982,0.0662,0.4635,0.0186</t>
-  </si>
-  <si>
-    <t>0.1356,0.0648,0.1535,0.7886</t>
-  </si>
-  <si>
-    <t>0.0045,0.9806,0.0115,0.0069</t>
-  </si>
-  <si>
-    <t>0.0187,0.9224,0.1091,0.0195</t>
-  </si>
-  <si>
-    <t>0.0026,0.9728,0.0088,0.0638</t>
-  </si>
-  <si>
-    <t>0.0020,0.8594,0.8658,0.0052</t>
-  </si>
-  <si>
-    <t>0.0816,0.8854,0.0956,0.0006</t>
-  </si>
-  <si>
-    <t>0.4601,0.6635,0.0098,0.0011</t>
-  </si>
-  <si>
-    <t>0.4944,0.6399,0.0119,0.0013</t>
-  </si>
-  <si>
-    <t>0.9859,0.0116,0.0009,0.0006</t>
-  </si>
-  <si>
-    <t>0.9858,0.0034,0.0012,0.0028</t>
-  </si>
-  <si>
-    <t>0.9933,0.0011,0.0002,0.0013</t>
-  </si>
-  <si>
-    <t>0.9575,0.0184,0.0008,0.0067</t>
-  </si>
-  <si>
-    <t>0.9929,0.0023,0.0010,0.0007</t>
-  </si>
-  <si>
-    <t>0.9849,0.0056,0.0074,0.0012</t>
-  </si>
-  <si>
-    <t>0.9806,0.0031,0.0011,0.0052</t>
-  </si>
-  <si>
-    <t>0.9700,0.0064,0.0007,0.0094</t>
-  </si>
-  <si>
-    <t>0.0067,0.7200,0.9313,0.0015</t>
-  </si>
-  <si>
-    <t>0.0070,0.6306,0.8807,0.0011</t>
-  </si>
-  <si>
-    <t>0.0099,0.3765,0.8883,0.0014</t>
-  </si>
-  <si>
-    <t>0.0942,0.2014,0.7226,0.0405</t>
-  </si>
-  <si>
-    <t>0.8310,0.0145,0.1203,0.0385</t>
-  </si>
-  <si>
-    <t>0.8532,0.0874,0.0218,0.0134</t>
-  </si>
-  <si>
-    <t>0.5242,0.0084,0.6490,0.0171</t>
-  </si>
-  <si>
-    <t>0.4894,0.0521,0.5772,0.0387</t>
-  </si>
-  <si>
-    <t>0.1314,0.0046,0.0077,0.9330</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.0007,0.9998</t>
-  </si>
-  <si>
-    <t>0.0003,0.0004,0.0056,0.9987</t>
-  </si>
-  <si>
-    <t>0.0289,0.0017,0.0007,0.9913</t>
-  </si>
-  <si>
-    <t>0.0004,0.9215,0.8706,0.0011</t>
-  </si>
-  <si>
-    <t>0.9762,0.0060,0.0029,0.0053</t>
-  </si>
-  <si>
-    <t>0.7150,0.3225,0.0312,0.0107</t>
-  </si>
-  <si>
-    <t>0.9830,0.0044,0.0023,0.0025</t>
-  </si>
-  <si>
-    <t>0.6123,0.5514,0.0047,0.0024</t>
-  </si>
-  <si>
-    <t>0.9790,0.0042,0.0049,0.0040</t>
-  </si>
-  <si>
-    <t>0.1700,0.0041,0.0393,0.8582</t>
-  </si>
-  <si>
-    <t>0.9839,0.0032,0.0016,0.0039</t>
-  </si>
-  <si>
-    <t>0.0063,0.3552,0.9278,0.0159</t>
-  </si>
-  <si>
-    <t>0.8711,0.0004,0.0057,0.1144</t>
-  </si>
-  <si>
-    <t>0.9224,0.0019,0.0081,0.0480</t>
-  </si>
-  <si>
-    <t>0.7170,0.3071,0.0360,0.0100</t>
-  </si>
-  <si>
-    <t>0.7699,0.1850,0.0107,0.0334</t>
-  </si>
-  <si>
-    <t>0.8530,0.1439,0.0231,0.0036</t>
-  </si>
-  <si>
-    <t>0.4762,0.5006,0.0650,0.0301</t>
-  </si>
-  <si>
-    <t>0.7096,0.3218,0.0127,0.0098</t>
-  </si>
-  <si>
-    <t>0.7359,0.3782,0.0091,0.0057</t>
-  </si>
-  <si>
-    <t>0.9957,0.0015,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9757,0.0035,0.0001,0.0075</t>
-  </si>
-  <si>
-    <t>0.9913,0.0019,0.0001,0.0015</t>
-  </si>
-  <si>
-    <t>0.9959,0.0007,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.9819,0.0041,0.0040,0.0031</t>
-  </si>
-  <si>
-    <t>0.9762,0.0047,0.0030,0.0047</t>
-  </si>
-  <si>
-    <t>0.9929,0.0011,0.0001,0.0016</t>
-  </si>
-  <si>
-    <t>0.9909,0.0018,0.0010,0.0016</t>
-  </si>
-  <si>
-    <t>0.3470,0.6933,0.0155,0.0099</t>
-  </si>
-  <si>
-    <t>0.7157,0.3824,0.0130,0.0020</t>
-  </si>
-  <si>
-    <t>0.3913,0.7321,0.0026,0.0018</t>
-  </si>
-  <si>
-    <t>0.8031,0.1144,0.1375,0.0195</t>
-  </si>
-  <si>
-    <t>0.9782,0.0222,0.0007,0.0007</t>
-  </si>
-  <si>
-    <t>0.9652,0.0097,0.0006,0.0083</t>
-  </si>
-  <si>
-    <t>0.9719,0.0362,0.0029,0.0004</t>
-  </si>
-  <si>
-    <t>0.9873,0.0030,0.0007,0.0022</t>
-  </si>
-  <si>
-    <t>0.0204,0.0248,0.9805,0.0012</t>
-  </si>
-  <si>
-    <t>0.9473,0.0576,0.0071,0.0013</t>
-  </si>
-  <si>
-    <t>0.0017,0.0059,0.9929,0.0020</t>
-  </si>
-  <si>
-    <t>0.0420,0.2958,0.8685,0.0222</t>
-  </si>
-  <si>
-    <t>0.0071,0.0070,0.9753,0.0285</t>
-  </si>
-  <si>
-    <t>0.0086,0.2123,0.9623,0.0057</t>
-  </si>
-  <si>
-    <t>0.0124,0.0154,0.9843,0.0003</t>
-  </si>
-  <si>
-    <t>0.0109,0.0022,0.9916,0.0005</t>
-  </si>
-  <si>
-    <t>0.0224,0.0126,0.9663,0.0079</t>
-  </si>
-  <si>
-    <t>0.0704,0.0076,0.9355,0.0138</t>
-  </si>
-  <si>
-    <t>0.0215,0.0083,0.9816,0.0008</t>
-  </si>
-  <si>
-    <t>0.4268,0.0727,0.5680,0.0062</t>
-  </si>
-  <si>
-    <t>0.6373,0.0870,0.3426,0.0062</t>
-  </si>
-  <si>
-    <t>0.2068,0.2483,0.6079,0.0141</t>
-  </si>
-  <si>
-    <t>0.5841,0.1267,0.3423,0.0058</t>
-  </si>
-  <si>
-    <t>0.5865,0.3175,0.1089,0.0480</t>
-  </si>
-  <si>
-    <t>0.2298,0.0250,0.8365,0.0121</t>
-  </si>
-  <si>
-    <t>0.9337,0.0880,0.0025,0.0017</t>
-  </si>
-  <si>
-    <t>0.8774,0.1971,0.0041,0.0005</t>
-  </si>
-  <si>
-    <t>0.9475,0.0836,0.0042,0.0004</t>
-  </si>
-  <si>
-    <t>0.9822,0.0236,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9681,0.0448,0.0015,0.0008</t>
-  </si>
-  <si>
-    <t>0.6445,0.0556,0.3983,0.0073</t>
-  </si>
-  <si>
-    <t>0.8969,0.0067,0.1422,0.0056</t>
-  </si>
-  <si>
-    <t>0.7946,0.0308,0.0588,0.0964</t>
-  </si>
-  <si>
-    <t>0.7052,0.0501,0.1492,0.1046</t>
-  </si>
-  <si>
-    <t>0.6897,0.0074,0.4126,0.0208</t>
-  </si>
-  <si>
-    <t>0.0081,0.0043,0.9761,0.0458</t>
-  </si>
-  <si>
-    <t>0.0064,0.3504,0.9394,0.0099</t>
-  </si>
-  <si>
-    <t>0.0155,0.2795,0.9206,0.0086</t>
-  </si>
-  <si>
-    <t>0.0345,0.0267,0.8511,0.1128</t>
-  </si>
-  <si>
-    <t>0.0432,0.6491,0.4852,0.0189</t>
-  </si>
-  <si>
-    <t>0.9938,0.0029,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9859,0.0057,0.0017,0.0018</t>
-  </si>
-  <si>
-    <t>0.9965,0.0010,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9922,0.0084,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9795,0.0199,0.0020,0.0006</t>
-  </si>
-  <si>
-    <t>0.9858,0.0080,0.0020,0.0009</t>
-  </si>
-  <si>
-    <t>0.9725,0.0302,0.0007,0.0010</t>
-  </si>
-  <si>
-    <t>0.9937,0.0047,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.0292,0.0370,0.9646,0.0025</t>
-  </si>
-  <si>
-    <t>0.6039,0.0556,0.5021,0.0151</t>
-  </si>
-  <si>
-    <t>0.9182,0.0351,0.0327,0.0125</t>
-  </si>
-  <si>
-    <t>0.0260,0.0163,0.9402,0.0237</t>
-  </si>
-  <si>
-    <t>0.0021,0.0205,0.9851,0.0018</t>
-  </si>
-  <si>
-    <t>0.0364,0.0547,0.9151,0.0026</t>
-  </si>
-  <si>
-    <t>0.0008,0.0031,0.9952,0.0026</t>
-  </si>
-  <si>
-    <t>0.0262,0.0440,0.9258,0.0056</t>
-  </si>
-  <si>
-    <t>0.0031,0.0035,0.9892,0.0069</t>
-  </si>
-  <si>
-    <t>0.0649,0.0618,0.8864,0.0179</t>
-  </si>
-  <si>
-    <t>0.0748,0.0185,0.9111,0.0139</t>
-  </si>
-  <si>
-    <t>0.3616,0.0017,0.1596,0.4035</t>
-  </si>
-  <si>
-    <t>0.8357,0.0049,0.2575,0.0068</t>
-  </si>
-  <si>
-    <t>0.8353,0.0084,0.2201,0.0049</t>
-  </si>
-  <si>
-    <t>0.9863,0.0106,0.0003,0.0007</t>
-  </si>
-  <si>
-    <t>0.9959,0.0016,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9971,0.0011,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9942,0.0034,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.9908,0.0024,0.0004,0.0015</t>
-  </si>
-  <si>
-    <t>0.9933,0.0039,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9891,0.0129,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9935,0.0030,0.0008,0.0004</t>
-  </si>
-  <si>
-    <t>0.0509,0.1214,0.9117,0.0038</t>
-  </si>
-  <si>
-    <t>0.0020,0.0215,0.9903,0.0013</t>
-  </si>
-  <si>
-    <t>0.1834,0.0402,0.7813,0.0359</t>
-  </si>
-  <si>
-    <t>0.1599,0.0343,0.7719,0.0018</t>
-  </si>
-  <si>
-    <t>0.0038,0.0033,0.9938,0.0006</t>
-  </si>
-  <si>
-    <t>0.2732,0.0261,0.5989,0.2050</t>
-  </si>
-  <si>
-    <t>0.1072,0.0049,0.9151,0.0224</t>
-  </si>
-  <si>
-    <t>0.0276,0.1185,0.8539,0.0294</t>
-  </si>
-  <si>
-    <t>0.6613,0.0009,0.0219,0.2817</t>
-  </si>
-  <si>
-    <t>0.0073,0.1866,0.0023,0.9850</t>
-  </si>
-  <si>
-    <t>0.0163,0.0056,0.0024,0.9921</t>
-  </si>
-  <si>
-    <t>0.0048,0.0004,0.0018,0.9962</t>
-  </si>
-  <si>
-    <t>0.0019,0.0004,0.0007,0.9986</t>
-  </si>
-  <si>
-    <t>0.7781,0.0637,0.0935,0.0787</t>
+    <t>0.9939,0.0020,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9968,0.0005,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.0026,0.0025,0.9947,0.0015</t>
+  </si>
+  <si>
+    <t>0.0835,0.0064,0.9370,0.0078</t>
+  </si>
+  <si>
+    <t>0.6806,0.0093,0.1105,0.1292</t>
+  </si>
+  <si>
+    <t>0.0163,0.0136,0.9706,0.0033</t>
+  </si>
+  <si>
+    <t>0.1562,0.8796,0.0080,0.0011</t>
+  </si>
+  <si>
+    <t>0.1263,0.9019,0.0082,0.0005</t>
+  </si>
+  <si>
+    <t>0.0639,0.9258,0.0012,0.0019</t>
+  </si>
+  <si>
+    <t>0.2967,0.8040,0.0019,0.0009</t>
+  </si>
+  <si>
+    <t>0.1426,0.8971,0.0055,0.0011</t>
+  </si>
+  <si>
+    <t>0.0907,0.9084,0.0018,0.0032</t>
+  </si>
+  <si>
+    <t>0.4017,0.7494,0.0025,0.0008</t>
+  </si>
+  <si>
+    <t>0.6514,0.0925,0.2683,0.1090</t>
+  </si>
+  <si>
+    <t>0.3350,0.0285,0.7727,0.0097</t>
+  </si>
+  <si>
+    <t>0.3408,0.4114,0.0604,0.1217</t>
+  </si>
+  <si>
+    <t>0.5601,0.0482,0.5600,0.0145</t>
+  </si>
+  <si>
+    <t>0.3224,0.1273,0.1997,0.5156</t>
+  </si>
+  <si>
+    <t>0.0062,0.9837,0.0060,0.0023</t>
+  </si>
+  <si>
+    <t>0.0193,0.9548,0.0179,0.0046</t>
+  </si>
+  <si>
+    <t>0.0088,0.9383,0.0222,0.0718</t>
+  </si>
+  <si>
+    <t>0.0050,0.9465,0.5023,0.0038</t>
+  </si>
+  <si>
+    <t>0.0519,0.9448,0.0300,0.0003</t>
+  </si>
+  <si>
+    <t>0.7962,0.2126,0.0302,0.0020</t>
+  </si>
+  <si>
+    <t>0.4067,0.6922,0.0075,0.0016</t>
+  </si>
+  <si>
+    <t>0.9794,0.0194,0.0017,0.0013</t>
+  </si>
+  <si>
+    <t>0.9839,0.0046,0.0009,0.0032</t>
+  </si>
+  <si>
+    <t>0.9959,0.0010,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9930,0.0015,0.0004,0.0011</t>
+  </si>
+  <si>
+    <t>0.9927,0.0019,0.0002,0.0013</t>
+  </si>
+  <si>
+    <t>0.9870,0.0063,0.0039,0.0009</t>
+  </si>
+  <si>
+    <t>0.9880,0.0022,0.0005,0.0024</t>
+  </si>
+  <si>
+    <t>0.9910,0.0021,0.0003,0.0013</t>
+  </si>
+  <si>
+    <t>0.0055,0.6466,0.8272,0.0082</t>
+  </si>
+  <si>
+    <t>0.0029,0.7785,0.7361,0.0002</t>
+  </si>
+  <si>
+    <t>0.0058,0.2586,0.9506,0.0003</t>
+  </si>
+  <si>
+    <t>0.0362,0.1183,0.9074,0.0012</t>
+  </si>
+  <si>
+    <t>0.8871,0.0663,0.0309,0.0043</t>
+  </si>
+  <si>
+    <t>0.7968,0.0588,0.0802,0.0479</t>
+  </si>
+  <si>
+    <t>0.3861,0.0051,0.7906,0.0087</t>
+  </si>
+  <si>
+    <t>0.3922,0.4800,0.1119,0.0669</t>
+  </si>
+  <si>
+    <t>0.2156,0.0034,0.0018,0.9023</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.0029,0.9993</t>
+  </si>
+  <si>
+    <t>0.0028,0.0037,0.0003,0.9985</t>
+  </si>
+  <si>
+    <t>0.0306,0.0020,0.0147,0.9750</t>
+  </si>
+  <si>
+    <t>0.0106,0.4518,0.9063,0.0018</t>
+  </si>
+  <si>
+    <t>0.9610,0.0183,0.0034,0.0057</t>
+  </si>
+  <si>
+    <t>0.5955,0.5322,0.0122,0.0022</t>
+  </si>
+  <si>
+    <t>0.9644,0.0331,0.0027,0.0015</t>
+  </si>
+  <si>
+    <t>0.8671,0.2418,0.0028,0.0006</t>
+  </si>
+  <si>
+    <t>0.9800,0.0050,0.0006,0.0050</t>
+  </si>
+  <si>
+    <t>0.2761,0.0153,0.0084,0.8575</t>
+  </si>
+  <si>
+    <t>0.9714,0.0026,0.0039,0.0109</t>
+  </si>
+  <si>
+    <t>0.0013,0.5973,0.8874,0.0063</t>
+  </si>
+  <si>
+    <t>0.9178,0.0013,0.0119,0.0431</t>
+  </si>
+  <si>
+    <t>0.9163,0.0031,0.0085,0.0567</t>
+  </si>
+  <si>
+    <t>0.7737,0.1934,0.0612,0.0045</t>
+  </si>
+  <si>
+    <t>0.7714,0.1846,0.0114,0.0254</t>
+  </si>
+  <si>
+    <t>0.8722,0.0978,0.0378,0.0027</t>
+  </si>
+  <si>
+    <t>0.7324,0.2810,0.0295,0.0069</t>
+  </si>
+  <si>
+    <t>0.8971,0.0794,0.0417,0.0027</t>
+  </si>
+  <si>
+    <t>0.7075,0.3613,0.0205,0.0026</t>
+  </si>
+  <si>
+    <t>0.9907,0.0019,0.0002,0.0017</t>
+  </si>
+  <si>
+    <t>0.9855,0.0073,0.0014,0.0013</t>
+  </si>
+  <si>
+    <t>0.9932,0.0030,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9958,0.0004,0.0002,0.0013</t>
+  </si>
+  <si>
+    <t>0.9897,0.0014,0.0002,0.0029</t>
+  </si>
+  <si>
+    <t>0.9752,0.0191,0.0017,0.0019</t>
+  </si>
+  <si>
+    <t>0.9939,0.0016,0.0005,0.0009</t>
+  </si>
+  <si>
+    <t>0.9831,0.0037,0.0005,0.0036</t>
+  </si>
+  <si>
+    <t>0.3862,0.7462,0.0027,0.0015</t>
+  </si>
+  <si>
+    <t>0.7768,0.3456,0.0051,0.0013</t>
+  </si>
+  <si>
+    <t>0.5589,0.5825,0.0071,0.0010</t>
+  </si>
+  <si>
+    <t>0.8495,0.0910,0.0980,0.0089</t>
+  </si>
+  <si>
+    <t>0.9537,0.0548,0.0052,0.0007</t>
+  </si>
+  <si>
+    <t>0.9794,0.0216,0.0011,0.0005</t>
+  </si>
+  <si>
+    <t>0.9491,0.0681,0.0050,0.0010</t>
+  </si>
+  <si>
+    <t>0.9630,0.0202,0.0035,0.0043</t>
+  </si>
+  <si>
+    <t>0.0054,0.0293,0.9913,0.0005</t>
+  </si>
+  <si>
+    <t>0.9699,0.0329,0.0012,0.0010</t>
+  </si>
+  <si>
+    <t>0.0038,0.0047,0.9918,0.0011</t>
+  </si>
+  <si>
+    <t>0.0250,0.4324,0.9094,0.0102</t>
+  </si>
+  <si>
+    <t>0.1195,0.0026,0.9426,0.0055</t>
+  </si>
+  <si>
+    <t>0.0087,0.0556,0.9725,0.0059</t>
+  </si>
+  <si>
+    <t>0.0056,0.0086,0.9865,0.0024</t>
+  </si>
+  <si>
+    <t>0.0307,0.0017,0.9823,0.0008</t>
+  </si>
+  <si>
+    <t>0.0235,0.0148,0.9589,0.0043</t>
+  </si>
+  <si>
+    <t>0.1304,0.0660,0.8422,0.0039</t>
+  </si>
+  <si>
+    <t>0.1899,0.0136,0.8866,0.0057</t>
+  </si>
+  <si>
+    <t>0.4911,0.0924,0.4920,0.0259</t>
+  </si>
+  <si>
+    <t>0.4325,0.0535,0.6564,0.0045</t>
+  </si>
+  <si>
+    <t>0.2832,0.0982,0.6334,0.0029</t>
+  </si>
+  <si>
+    <t>0.6131,0.1230,0.2806,0.0679</t>
+  </si>
+  <si>
+    <t>0.5040,0.1758,0.3913,0.0390</t>
+  </si>
+  <si>
+    <t>0.4234,0.0294,0.6841,0.0071</t>
+  </si>
+  <si>
+    <t>0.7234,0.4089,0.0075,0.0005</t>
+  </si>
+  <si>
+    <t>0.7543,0.2295,0.0280,0.0005</t>
+  </si>
+  <si>
+    <t>0.9661,0.0416,0.0047,0.0002</t>
+  </si>
+  <si>
+    <t>0.9806,0.0163,0.0023,0.0011</t>
+  </si>
+  <si>
+    <t>0.9213,0.1301,0.0026,0.0006</t>
+  </si>
+  <si>
+    <t>0.5193,0.3341,0.1586,0.0448</t>
+  </si>
+  <si>
+    <t>0.7886,0.0129,0.2668,0.0142</t>
+  </si>
+  <si>
+    <t>0.7282,0.0659,0.0457,0.1194</t>
+  </si>
+  <si>
+    <t>0.8121,0.0037,0.2566,0.0099</t>
+  </si>
+  <si>
+    <t>0.8401,0.0103,0.1957,0.0090</t>
+  </si>
+  <si>
+    <t>0.6132,0.0544,0.3204,0.0909</t>
+  </si>
+  <si>
+    <t>0.0752,0.1082,0.6774,0.1533</t>
+  </si>
+  <si>
+    <t>0.0192,0.0734,0.9444,0.0076</t>
+  </si>
+  <si>
+    <t>0.1806,0.1210,0.7669,0.0113</t>
+  </si>
+  <si>
+    <t>0.0606,0.0795,0.8803,0.0122</t>
+  </si>
+  <si>
+    <t>0.9742,0.0148,0.0008,0.0024</t>
+  </si>
+  <si>
+    <t>0.9881,0.0066,0.0011,0.0007</t>
+  </si>
+  <si>
+    <t>0.9910,0.0016,0.0000,0.0017</t>
+  </si>
+  <si>
+    <t>0.9893,0.0023,0.0007,0.0019</t>
+  </si>
+  <si>
+    <t>0.9823,0.0174,0.0011,0.0006</t>
+  </si>
+  <si>
+    <t>0.9923,0.0057,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9931,0.0014,0.0001,0.0011</t>
+  </si>
+  <si>
+    <t>0.9887,0.0047,0.0025,0.0012</t>
+  </si>
+  <si>
+    <t>0.0348,0.0126,0.9715,0.0014</t>
+  </si>
+  <si>
+    <t>0.3664,0.0756,0.6879,0.0273</t>
+  </si>
+  <si>
+    <t>0.8927,0.0423,0.0375,0.0217</t>
+  </si>
+  <si>
+    <t>0.0017,0.0052,0.9953,0.0009</t>
+  </si>
+  <si>
+    <t>0.0002,0.0011,0.9956,0.0106</t>
+  </si>
+  <si>
+    <t>0.0241,0.0216,0.9564,0.0004</t>
+  </si>
+  <si>
+    <t>0.0015,0.0040,0.9958,0.0008</t>
+  </si>
+  <si>
+    <t>0.1831,0.0955,0.7241,0.0113</t>
+  </si>
+  <si>
+    <t>0.0015,0.0059,0.9936,0.0016</t>
+  </si>
+  <si>
+    <t>0.0216,0.0343,0.9528,0.0035</t>
+  </si>
+  <si>
+    <t>0.3464,0.0215,0.6910,0.0495</t>
+  </si>
+  <si>
+    <t>0.4201,0.0035,0.7149,0.0186</t>
+  </si>
+  <si>
+    <t>0.6336,0.0320,0.3122,0.0917</t>
+  </si>
+  <si>
+    <t>0.6661,0.0015,0.3639,0.0201</t>
+  </si>
+  <si>
+    <t>0.9945,0.0020,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9906,0.0092,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9935,0.0076,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9861,0.0082,0.0021,0.0007</t>
+  </si>
+  <si>
+    <t>0.9945,0.0023,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9946,0.0035,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9907,0.0069,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9912,0.0019,0.0003,0.0015</t>
+  </si>
+  <si>
+    <t>0.0052,0.0428,0.9791,0.0006</t>
+  </si>
+  <si>
+    <t>0.0069,0.0139,0.9886,0.0011</t>
+  </si>
+  <si>
+    <t>0.0190,0.1400,0.8833,0.0215</t>
+  </si>
+  <si>
+    <t>0.1175,0.0622,0.7281,0.0092</t>
+  </si>
+  <si>
+    <t>0.0055,0.0037,0.9867,0.0074</t>
+  </si>
+  <si>
+    <t>0.0370,0.0202,0.9414,0.0367</t>
+  </si>
+  <si>
+    <t>0.1455,0.0116,0.8902,0.0101</t>
+  </si>
+  <si>
+    <t>0.0188,0.0026,0.6121,0.5689</t>
+  </si>
+  <si>
+    <t>0.5387,0.0008,0.0026,0.6788</t>
+  </si>
+  <si>
+    <t>0.0764,0.0113,0.0057,0.9609</t>
+  </si>
+  <si>
+    <t>0.0644,0.0034,0.0012,0.9805</t>
+  </si>
+  <si>
+    <t>0.0009,0.0001,0.0122,0.9968</t>
+  </si>
+  <si>
+    <t>0.0005,0.0004,0.0006,0.9994</t>
+  </si>
+  <si>
+    <t>0.6974,0.0462,0.0232,0.2464</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1974,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1988,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,10 +1999,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2016,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2030,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2044,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2058,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2072,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2086,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2100,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2114,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2128,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2127,7 +2142,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2141,7 +2156,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,10 +2167,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2184,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,10 +2195,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2212,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2226,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,10 +2237,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2254,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2268,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,10 +2279,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,10 +2293,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2310,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2324,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2338,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2352,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2366,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,10 +2377,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2379,7 +2394,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2408,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,10 +2419,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2436,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,10 +2447,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,10 +2461,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2478,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,10 +2489,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2506,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2520,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2534,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2548,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2562,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2576,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2587,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2604,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2618,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2632,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2646,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,7 +2660,7 @@
         <v>263</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2674,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2688,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2702,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2716,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2730,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2744,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2758,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2772,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2786,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2800,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2814,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2828,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2842,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2856,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2870,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2884,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2898,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2912,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2911,7 +2926,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2925,7 +2940,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2954,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2968,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,10 +2979,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,7 +2996,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2995,7 +3010,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3024,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3038,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3052,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3066,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3080,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3094,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,10 +3105,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,7 +3122,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,10 +3133,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,10 +3147,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,7 +3164,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,10 +3175,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3192,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3206,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3220,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3234,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3248,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3262,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3276,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3290,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3304,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3318,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3332,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3346,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3360,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3374,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3388,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3402,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3416,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3430,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3429,7 +3444,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3458,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3472,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3486,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3500,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3514,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3528,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3542,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,10 +3553,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3555,7 +3570,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3569,7 +3584,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,10 +3595,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,10 +3609,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3611,7 +3626,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3640,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3654,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3668,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,7 +3682,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3696,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,10 +3707,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3709,7 +3724,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3738,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3752,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3766,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3780,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3794,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3808,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3822,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3836,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3835,7 +3850,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3849,7 +3864,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3863,7 +3878,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3892,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3906,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3905,7 +3920,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3919,7 +3934,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,10 +3945,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3962,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3976,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3990,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +4004,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,10 +4015,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4032,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,10 +4043,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4060,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,10 +4071,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4088,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4087,7 +4102,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4116,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,10 +4127,10 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4129,7 +4144,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4158,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4157,7 +4172,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4186,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4200,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,10 +4211,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4228,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4242,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4256,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4270,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4284,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4298,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4312,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4326,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4340,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4354,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4353,7 +4368,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4367,7 +4382,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,10 +4393,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4395,7 +4410,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4424,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4438,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4452,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4466,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4480,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4494,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4508,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4522,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4536,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4550,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4564,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4578,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4592,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4591,7 +4606,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4620,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,10 +4631,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,10 +4645,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4647,7 +4662,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4661,7 +4676,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4675,7 +4690,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4689,7 +4704,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,7 +4718,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4717,7 +4732,7 @@
         <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4731,7 +4746,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4760,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4759,7 +4774,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4773,7 +4788,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4802,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4801,7 +4816,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4815,7 +4830,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4829,7 +4844,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,10 +4855,10 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4872,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4886,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4900,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,10 +4911,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4928,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4942,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4956,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4970,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4984,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4998,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5012,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5026,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5040,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5039,7 +5054,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5068,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5082,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5096,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5110,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5124,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5138,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5152,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5166,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5180,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,10 +5191,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5193,7 +5208,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5222,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5236,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5250,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5264,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5278,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5292,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5306,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5320,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5334,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5348,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5362,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5376,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5390,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5404,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5403,7 +5418,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5432,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,10 +5443,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,10 +5457,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5474,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5488,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5502,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5516,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5515,7 +5530,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
     </row>
   </sheetData>
